--- a/Shared/XLS/Option.xlsx
+++ b/Shared/XLS/Option.xlsx
@@ -263,28 +263,36 @@
     <t>StatDetail_DamageTakenAmp_Add</t>
   </si>
   <si>
-    <t>OPT_LEARN_DualBlades_Active_01</t>
-  </si>
-  <si>
-    <t>Skill_DualBlades_Active_01</t>
-  </si>
-  <si>
-    <t>OPT_DMG_DualBlades_Active_01</t>
-  </si>
-  <si>
-    <t>SKM_DualBlades_Active_01_Ratio</t>
-  </si>
-  <si>
-    <t>OPT_APPEND_DualBlades_AtkSpeedBuff</t>
-  </si>
-  <si>
-    <t>SKM_DualBlades_Active_01_AppendAtkSpeedBuff</t>
-  </si>
-  <si>
-    <t>OPT_ATKSPEED_DualBlades_Buff</t>
-  </si>
-  <si>
-    <t>SKM_DualBlades_AtkSpeedBuff_Ratio</t>
+    <t>OPT_LEARN_GreatSword_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_DMG_GreatSword_Active_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKM_GreatSword_Active_01_Ratio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_APPEND_GreatSword_AtkSpeedBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKM_GreatSword_Active_01_AppendAtkSpeedBuff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_ATKSPEED_GreatSword_Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKM_GreatSword_AtkSpeedBuff_Ratio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -799,7 +807,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
